--- a/data/trans_orig/PCS12_SP-Edad-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media del componente de salud física (SF12)</t>
+          <t>Puntuación media del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,22; 55,76</t>
+          <t>55,2; 55,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,15; 55,83</t>
+          <t>55,13; 55,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,74; 56,31</t>
+          <t>55,75; 56,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,45; 56,23</t>
+          <t>55,45; 56,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,62; 55,41</t>
+          <t>54,67; 55,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,54; 55,43</t>
+          <t>54,56; 55,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,4; 56,02</t>
+          <t>55,4; 56,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,63; 55,99</t>
+          <t>54,61; 55,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,03; 55,51</t>
+          <t>55,05; 55,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55,0; 55,55</t>
+          <t>54,99; 55,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,68; 56,11</t>
+          <t>55,69; 56,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,27; 56,01</t>
+          <t>55,26; 56,02</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,97; 55,65</t>
+          <t>55,0; 55,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,65; 55,41</t>
+          <t>54,65; 55,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,15; 55,85</t>
+          <t>55,13; 55,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,13; 54,67</t>
+          <t>53,15; 54,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,84; 54,7</t>
+          <t>53,85; 54,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,43; 55,2</t>
+          <t>54,44; 55,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,31; 55,29</t>
+          <t>54,3; 55,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,41; 55,26</t>
+          <t>54,42; 55,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,57; 55,1</t>
+          <t>54,61; 55,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,66; 55,2</t>
+          <t>54,65; 55,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,89; 55,52</t>
+          <t>54,88; 55,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,01; 54,87</t>
+          <t>53,99; 54,87</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,18; 54,91</t>
+          <t>54,17; 54,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,87; 54,73</t>
+          <t>53,86; 54,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,5; 55,27</t>
+          <t>54,49; 55,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,25; 54,28</t>
+          <t>53,19; 54,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,65; 53,64</t>
+          <t>52,63; 53,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,61; 53,67</t>
+          <t>52,61; 53,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,58; 54,52</t>
+          <t>53,55; 54,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,46; 53,51</t>
+          <t>52,48; 53,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,54; 54,17</t>
+          <t>53,52; 54,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,32; 54,05</t>
+          <t>53,36; 54,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,17; 54,82</t>
+          <t>54,17; 54,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,03; 53,76</t>
+          <t>53,05; 53,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,8; 53,93</t>
+          <t>52,87; 53,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,68; 53,82</t>
+          <t>52,68; 53,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,0; 53,43</t>
+          <t>52,09; 53,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,53; 52,03</t>
+          <t>49,61; 52,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,39; 51,84</t>
+          <t>50,52; 51,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,89; 52,34</t>
+          <t>50,91; 52,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,26; 52,71</t>
+          <t>51,32; 52,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,72; 52,12</t>
+          <t>50,79; 52,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,87; 52,77</t>
+          <t>51,84; 52,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,03; 52,96</t>
+          <t>51,99; 52,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,91; 52,9</t>
+          <t>51,93; 52,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,06; 51,72</t>
+          <t>50,19; 51,77</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,17; 50,87</t>
+          <t>49,23; 50,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,67; 51,47</t>
+          <t>49,76; 51,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,19; 51,85</t>
+          <t>50,28; 51,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,32; 49,84</t>
+          <t>48,34; 49,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,78; 49,66</t>
+          <t>47,76; 49,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,23; 48,25</t>
+          <t>46,12; 48,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,13; 49,19</t>
+          <t>47,21; 49,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,59; 48,98</t>
+          <t>47,59; 48,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,69; 50,01</t>
+          <t>48,69; 50,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,15; 49,56</t>
+          <t>48,21; 49,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,94; 50,29</t>
+          <t>48,96; 50,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,19; 49,27</t>
+          <t>48,23; 49,29</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,15; 49,32</t>
+          <t>47,18; 49,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,32; 48,1</t>
+          <t>45,5; 48,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,43; 49,6</t>
+          <t>47,51; 49,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48,3; 49,86</t>
+          <t>48,18; 49,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,19; 44,42</t>
+          <t>42,25; 44,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,55; 44,07</t>
+          <t>41,53; 44,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,45; 45,81</t>
+          <t>43,34; 45,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,62; 51,08</t>
+          <t>45,68; 51,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,86; 46,42</t>
+          <t>44,76; 46,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43,88; 45,71</t>
+          <t>43,89; 45,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45,68; 47,33</t>
+          <t>45,66; 47,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47,28; 50,62</t>
+          <t>47,25; 50,84</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,37; 43,5</t>
+          <t>40,33; 43,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,29; 41,47</t>
+          <t>38,34; 41,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,39; 44,11</t>
+          <t>41,51; 44,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,12; 44,48</t>
+          <t>42,26; 44,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,06; 39,53</t>
+          <t>37,08; 39,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,51; 36,89</t>
+          <t>34,54; 36,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,57; 39,44</t>
+          <t>36,64; 39,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,76; 37,39</t>
+          <t>35,78; 37,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,77; 40,82</t>
+          <t>38,83; 40,71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36,34; 38,37</t>
+          <t>36,37; 38,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38,87; 40,97</t>
+          <t>38,83; 40,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,65; 39,97</t>
+          <t>38,61; 40,06</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,55; 53,04</t>
+          <t>52,53; 53,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,95; 52,53</t>
+          <t>51,96; 52,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,42; 52,96</t>
+          <t>52,38; 52,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,7; 51,6</t>
+          <t>50,61; 51,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,02; 50,67</t>
+          <t>50,03; 50,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,42; 50,09</t>
+          <t>49,38; 50,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,01; 50,74</t>
+          <t>50,04; 50,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,33; 50,37</t>
+          <t>49,35; 50,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,33; 51,77</t>
+          <t>51,35; 51,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50,74; 51,23</t>
+          <t>50,74; 51,19</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51,29; 51,78</t>
+          <t>51,29; 51,75</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,23; 50,84</t>
+          <t>50,23; 50,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/PCS12_SP-Edad-trans_orig.xlsx
+++ b/data/trans_orig/PCS12_SP-Edad-trans_orig.xlsx
@@ -663,47 +663,47 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>55,84</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,06</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55,05</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>55,75</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>55,16</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>55,3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55,29</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>55,91</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,06</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55,05</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,75</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>55,41</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>55,3</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>55,29</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>55,91</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,69</t>
+          <t>55,52</t>
         </is>
       </c>
     </row>
@@ -716,27 +716,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,2; 55,77</t>
+          <t>55,23; 55,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,13; 55,82</t>
+          <t>55,14; 55,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,75; 56,29</t>
+          <t>55,76; 56,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55,45; 56,24</t>
+          <t>55,43; 56,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,67; 55,39</t>
+          <t>54,7; 55,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,32 +746,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,4; 56,06</t>
+          <t>55,4; 56,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,61; 55,97</t>
+          <t>54,3; 55,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55,05; 55,53</t>
+          <t>55,05; 55,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,99; 55,56</t>
+          <t>55,0; 55,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55,69; 56,11</t>
+          <t>55,69; 56,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,26; 56,02</t>
+          <t>55,13; 55,86</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54,03</t>
+          <t>54,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54,88</t>
+          <t>54,84</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,49</t>
+          <t>54,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,0; 55,65</t>
+          <t>55,01; 55,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,65; 55,39</t>
+          <t>54,63; 55,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,13; 55,89</t>
+          <t>55,12; 55,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,15; 54,63</t>
+          <t>53,27; 54,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,85; 54,69</t>
+          <t>53,81; 54,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,44; 55,22</t>
+          <t>54,46; 55,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,3; 55,31</t>
+          <t>54,36; 55,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,42; 55,25</t>
+          <t>54,36; 55,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,61; 55,11</t>
+          <t>54,58; 55,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54,65; 55,21</t>
+          <t>54,68; 55,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54,88; 55,5</t>
+          <t>54,88; 55,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,99; 54,87</t>
+          <t>54,05; 54,86</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53,81</t>
+          <t>53,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>53,03</t>
+          <t>53,1</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,42</t>
+          <t>53,54</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,17; 54,9</t>
+          <t>54,17; 54,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,86; 54,72</t>
+          <t>53,76; 54,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,49; 55,29</t>
+          <t>54,49; 55,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,19; 54,27</t>
+          <t>53,5; 54,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,63; 53,66</t>
+          <t>52,7; 53,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,61; 53,6</t>
+          <t>52,63; 53,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,55; 54,52</t>
+          <t>53,58; 54,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,48; 53,53</t>
+          <t>52,55; 53,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53,52; 54,16</t>
+          <t>53,52; 54,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,36; 54,05</t>
+          <t>53,35; 54,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,17; 54,8</t>
+          <t>54,15; 54,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>53,05; 53,78</t>
+          <t>53,17; 53,85</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50,9</t>
+          <t>51,72</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>51,35</t>
+          <t>51,22</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,1</t>
+          <t>51,46</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,87; 53,92</t>
+          <t>52,88; 53,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,68; 53,84</t>
+          <t>52,69; 53,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52,09; 53,41</t>
+          <t>52,07; 53,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,61; 52,08</t>
+          <t>50,95; 52,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,52; 51,89</t>
+          <t>50,52; 51,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,91; 52,31</t>
+          <t>50,83; 52,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,32; 52,71</t>
+          <t>51,33; 52,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,79; 52,18</t>
+          <t>50,75; 51,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,84; 52,72</t>
+          <t>51,86; 52,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51,93; 52,91</t>
+          <t>51,9; 52,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,19; 51,77</t>
+          <t>51,03; 51,86</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49,17</t>
+          <t>49,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48,31</t>
+          <t>48,25</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,74</t>
+          <t>48,83</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>49,23; 50,91</t>
+          <t>49,14; 50,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,76; 51,47</t>
+          <t>49,62; 51,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50,28; 51,97</t>
+          <t>50,28; 52,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,34; 49,92</t>
+          <t>48,61; 50,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,76; 49,71</t>
+          <t>47,9; 49,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,12; 48,15</t>
+          <t>46,24; 48,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,21; 49,07</t>
+          <t>47,2; 49,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,59; 48,9</t>
+          <t>47,58; 48,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,69; 50,04</t>
+          <t>48,67; 49,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,21; 49,59</t>
+          <t>48,12; 49,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,96; 50,32</t>
+          <t>48,94; 50,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,23; 49,29</t>
+          <t>48,3; 49,32</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49,14</t>
+          <t>49,32</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>48,35</t>
+          <t>45,79</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,65</t>
+          <t>47,48</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,18; 49,31</t>
+          <t>47,32; 49,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,5; 48,17</t>
+          <t>45,48; 48,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47,51; 49,61</t>
+          <t>47,43; 49,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48,18; 49,81</t>
+          <t>48,54; 50,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,25; 44,48</t>
+          <t>42,14; 44,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,53; 44,07</t>
+          <t>41,58; 44,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,34; 45,72</t>
+          <t>43,49; 45,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,68; 51,22</t>
+          <t>45,08; 46,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,76; 46,49</t>
+          <t>44,81; 46,36</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43,89; 45,61</t>
+          <t>43,77; 45,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45,66; 47,35</t>
+          <t>45,61; 47,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>47,25; 50,84</t>
+          <t>46,92; 48,0</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43,35</t>
+          <t>43,42</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,31</t>
+          <t>39,35</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,33; 43,46</t>
+          <t>40,36; 43,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>38,34; 41,53</t>
+          <t>38,11; 41,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,51; 44,05</t>
+          <t>41,39; 44,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42,26; 44,45</t>
+          <t>42,34; 44,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>37,08; 39,6</t>
+          <t>37,14; 39,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,54; 36,87</t>
+          <t>34,55; 36,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,64; 39,39</t>
+          <t>36,64; 39,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,78; 37,43</t>
+          <t>35,79; 37,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,83; 40,71</t>
+          <t>38,75; 40,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36,37; 38,3</t>
+          <t>36,37; 38,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38,83; 40,86</t>
+          <t>38,88; 40,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,61; 40,06</t>
+          <t>38,64; 40,07</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51,24</t>
+          <t>51,52</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>49,8</t>
+          <t>49,49</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50,5</t>
+          <t>50,48</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>52,53; 53,07</t>
+          <t>52,55; 53,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,96; 52,56</t>
+          <t>51,94; 52,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,38; 52,96</t>
+          <t>52,4; 52,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50,61; 51,6</t>
+          <t>51,24; 51,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,03; 50,66</t>
+          <t>50,01; 50,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,38; 50,11</t>
+          <t>49,41; 50,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,04; 50,73</t>
+          <t>49,97; 50,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>49,35; 50,43</t>
+          <t>49,18; 49,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51,35; 51,77</t>
+          <t>51,34; 51,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50,74; 51,19</t>
+          <t>50,73; 51,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51,29; 51,75</t>
+          <t>51,29; 51,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,23; 50,85</t>
+          <t>50,28; 50,69</t>
         </is>
       </c>
     </row>
